--- a/output/pdf_financials_xlsx/Y.xlsx
+++ b/output/pdf_financials_xlsx/Y.xlsx
@@ -1866,10 +1866,10 @@
         <v>102.776</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>67.253</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>17.26</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -1878,19 +1878,19 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>123.559</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>43.907</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>23.229</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>44.204</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>62.681</v>
       </c>
     </row>
     <row r="35">
@@ -1946,10 +1946,10 @@
         <v>102.776</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>67.253</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>17.26</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -1958,19 +1958,19 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>123.559</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>43.907</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>23.229</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>44.204</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>62.681</v>
       </c>
     </row>
     <row r="37">
@@ -2426,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>140.389</v>
+        <v>73.136</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>90.395</v>
+        <v>73.13500000000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>33.775</v>
@@ -2438,19 +2438,19 @@
         <v>62.356</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>131.126</v>
+        <v>7.567</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>51.091</v>
+        <v>7.184</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>31.703</v>
+        <v>8.474</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>53.233</v>
+        <v>9.029</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>71.869</v>
+        <v>9.188000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/Y.xlsx
+++ b/output/pdf_financials_xlsx/Y.xlsx
@@ -19826,7 +19826,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="n">
         <v>-54.584</v>
       </c>

--- a/output/pdf_financials_xlsx/Y.xlsx
+++ b/output/pdf_financials_xlsx/Y.xlsx
@@ -1046,15 +1046,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-531.058</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>52.009</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>59.914</v>
@@ -1258,15 +1254,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-594.482</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>82.809</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>70.63500000000001</v>
@@ -1388,15 +1380,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-594.482</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>82.809</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>70.63500000000001</v>
@@ -1536,15 +1524,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>26.397957</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>29.78741</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>26.755682</v>
@@ -1582,15 +1566,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>-531.058</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>52.009</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>59.914</v>
@@ -1670,15 +1650,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>-418.093</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>128.103</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>79.54900000000001</v>
@@ -1722,15 +1698,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F30" s="3" t="n">
+        <v>-57.43296056002538</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>22.19405920009702</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>27.65517337282632</v>
@@ -1768,15 +1740,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-11.94295161733747</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>59.22051952546674</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>17.89398137330173</v>
@@ -1820,15 +1788,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F32" s="3" t="n">
+        <v>-81.66331715586008</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>14.34679787593448</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>24.55622536033875</v>
@@ -3334,25 +3298,25 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>9.045</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>1.888</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>3.396</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>3.967</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>3.778</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>3.941</v>
       </c>
     </row>
     <row r="71">
@@ -3374,25 +3338,25 @@
         <v>75.161</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>9.045</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>1.888</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>3.396</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>3.967</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>3.778</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>3.941</v>
       </c>
     </row>
     <row r="72">
@@ -3534,25 +3498,25 @@
         <v>53.01</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>135.89</v>
+        <v>126.845</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>102.078</v>
+        <v>100.19</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>29.335</v>
+        <v>26.395</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>21.125</v>
+        <v>17.729</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>20.494</v>
+        <v>16.527</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>19.863</v>
+        <v>16.085</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>16.759</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="76">
@@ -3654,25 +3618,25 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>52.607</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>84.291</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>46.939</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>43.733</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>39.947</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>36.16</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>32.194</v>
       </c>
     </row>
     <row r="79">
@@ -3694,25 +3658,25 @@
         <v>234.867</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>52.607</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>84.291</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>46.939</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0</v>
+        <v>43.733</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0</v>
+        <v>39.947</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0</v>
+        <v>36.16</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>32.194</v>
       </c>
     </row>
     <row r="80">
@@ -3733,40 +3697,26 @@
       <c r="E80" s="3" t="n">
         <v>0.8404029232537462</v>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>0.1568848988233378</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-0.4311558492888197</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.4295063333649068</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.7164530791565954</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>1.03923703142749</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.7423420074349443</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.6970620575242578</v>
       </c>
     </row>
     <row r="81">
@@ -3948,25 +3898,25 @@
         <v>269.575</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>543.912</v>
+        <v>491.305</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>608.171</v>
+        <v>523.88</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>123.21</v>
+        <v>76.271</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>85.503</v>
+        <v>41.77</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>75.678</v>
+        <v>35.731</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>65.399</v>
+        <v>29.239</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>71.723</v>
+        <v>39.529</v>
       </c>
     </row>
     <row r="86">
@@ -4482,15 +4432,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-594.482</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>82.809</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>70.63500000000001</v>
@@ -7328,7 +7274,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -7578,7 +7528,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8145,7 +8099,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -10151,7 +10109,11 @@
           <t>Current portion of lease obligations (Note 8) 4,352</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -10569,7 +10531,11 @@
           <t>Lease obligations (Note 8) 70,968</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -30691,7 +30657,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
